--- a/data/single_run/input/casualty_generation_settings/military_force_structure/force_structure_second_test.xlsx
+++ b/data/single_run/input/casualty_generation_settings/military_force_structure/force_structure_second_test.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,43 +413,78 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>division</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>brigade</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>battalion</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>par</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>involved</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>bcas_spawning_points</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>dnbi_spawning_points</t>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ccp_ids</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>r1_ids</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>r2b_ids</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>r2e_ids</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>axp_ids</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>neighbor_r1_ids</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>neighbor_r2b_ids</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>neighbor_r2e_ids</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>neighbor_axp_ids</t>
         </is>
       </c>
     </row>
@@ -489,7 +512,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ccp_br1_bt1_1,ccp_br1_bt1_2,ccp_br1_bt1_3,ccp_br1_bt1_4,ccp_br1_bt1_5,ccp_br1_bt1_6,ccp_br1_bt1_7,ccp_br1_bt1_8,ccp_br1_bt1_9</t>
+          <t>ccp_br1_bt1_1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -497,39 +520,13 @@
           <t>r1_br1_bt1_1</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>DIV1</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>BR1</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>BR1_BT2</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>900</v>
-      </c>
-      <c r="E3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>ccp_br1_bt2_1,ccp_br1_bt2_2,ccp_br1_bt2_3,ccp_br1_bt2_4,ccp_br1_bt2_5,ccp_br1_bt2_6,ccp_br1_bt2_7,ccp_br1_bt2_8,ccp_br1_bt2_9</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>r1_br1_bt2_1</t>
-        </is>
-      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
